--- a/Result/profitability/3128.xlsx
+++ b/Result/profitability/3128.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3775</v>
+        <v>0.33</v>
       </c>
       <c r="N2" t="n">
-        <v>30.605</v>
+        <v>29.98625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.38125</v>
+        <v>0.27625</v>
       </c>
       <c r="N3" t="n">
-        <v>28.52375</v>
+        <v>27.4925</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33125</v>
+        <v>0.25375</v>
       </c>
       <c r="N4" t="n">
-        <v>26.0875</v>
+        <v>25.03125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.29375</v>
+        <v>0.30375</v>
       </c>
       <c r="N5" t="n">
-        <v>24.33</v>
+        <v>23.695</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.34875</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>22.79625</v>
+        <v>22.27375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,13 +1264,13 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.33875</v>
+        <v>0.26875</v>
       </c>
       <c r="N7" t="n">
-        <v>21.5925</v>
+        <v>20.6125</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3175</v>
+        <v>0.275</v>
       </c>
       <c r="N8" t="n">
-        <v>19.88875</v>
+        <v>19.35</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>215</v>
+      </c>
+      <c r="D75" t="n">
+        <v>158</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.7625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.096774193548387</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.310000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1404366243075921</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7272727272727273</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.080000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1614748887476161</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
